--- a/data/trans_orig/Q31A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q31A-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Edad media en que comenzó a tomar bebidas alcohólicas de forma regular</t>
+          <t>Edad media en que comenzó a tomar bebidas alcohólicas de forma regular (tasa de respuesta: 98,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,57 +721,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,96; 16,34</t>
+          <t>15,94; 16,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,93; 16,31</t>
+          <t>15,95; 16,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,09; 16,74</t>
+          <t>16,03; 16,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,23; 16,67</t>
+          <t>16,24; 16,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,01; 16,46</t>
+          <t>16,02; 16,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,24; 16,72</t>
+          <t>16,23; 16,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,72; 16,57</t>
+          <t>15,7; 16,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,99; 16,31</t>
+          <t>15,99; 16,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,02; 16,33</t>
+          <t>16,04; 16,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,13; 16,43</t>
+          <t>16,13; 16,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,06; 16,58</t>
+          <t>16,07; 16,56</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,71; 17,06</t>
+          <t>16,73; 17,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -866,32 +866,32 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,65; 17,06</t>
+          <t>16,66; 17,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,52; 17,06</t>
+          <t>16,52; 17,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,62</t>
+          <t>17,2; 17,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,22; 17,86</t>
+          <t>17,19; 17,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,18; 17,82</t>
+          <t>17,17; 17,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,53; 17,32</t>
+          <t>16,56; 17,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,0; 17,34</t>
+          <t>16,97; 17,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,92; 17,26</t>
+          <t>16,91; 17,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,6; 17,04</t>
+          <t>16,6; 17,05</t>
         </is>
       </c>
     </row>
@@ -996,52 +996,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,99; 17,35</t>
+          <t>17,01; 17,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,06; 17,52</t>
+          <t>17,06; 17,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,87; 17,36</t>
+          <t>16,86; 17,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,94; 17,54</t>
+          <t>16,94; 17,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,0; 18,83</t>
+          <t>17,98; 18,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,36; 19,18</t>
+          <t>18,36; 19,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,57; 18,43</t>
+          <t>17,57; 18,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,9; 18,9</t>
+          <t>17,96; 19,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,41; 17,8</t>
+          <t>17,42; 17,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,6; 18,02</t>
+          <t>17,6; 18,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,37; 17,94</t>
+          <t>17,36; 17,88</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,18; 17,61</t>
+          <t>17,19; 17,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,47; 18,07</t>
+          <t>17,49; 18,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,99; 17,53</t>
+          <t>17,0; 17,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,48</t>
+          <t>16,82; 17,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,96; 20,13</t>
+          <t>18,97; 20,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,9; 20,13</t>
+          <t>18,89; 20,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,61; 19,78</t>
+          <t>18,62; 19,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,39; 19,64</t>
+          <t>18,35; 19,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,8; 18,31</t>
+          <t>17,84; 18,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,08; 18,67</t>
+          <t>18,08; 18,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,74; 18,33</t>
+          <t>17,74; 18,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,46; 18,09</t>
+          <t>17,44; 18,04</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,32; 17,98</t>
+          <t>17,33; 17,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,52; 18,95</t>
+          <t>17,54; 19,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,71; 17,34</t>
+          <t>16,74; 17,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,18; 17,99</t>
+          <t>17,18; 18,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,22; 20,69</t>
+          <t>19,15; 20,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,8; 22,43</t>
+          <t>19,8; 22,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,46; 21,64</t>
+          <t>19,39; 21,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,33; 21,25</t>
+          <t>19,43; 21,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,98; 18,67</t>
+          <t>17,98; 18,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,39; 19,6</t>
+          <t>18,39; 19,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,74; 18,63</t>
+          <t>17,7; 18,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,05; 18,9</t>
+          <t>18,06; 18,9</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,7; 18,76</t>
+          <t>17,71; 18,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,48; 18,5</t>
+          <t>17,52; 18,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,89; 18,24</t>
+          <t>16,92; 18,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,81; 17,43</t>
+          <t>16,81; 17,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,53; 20,4</t>
+          <t>18,5; 20,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,94; 25,79</t>
+          <t>20,93; 25,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,79; 26,9</t>
+          <t>20,7; 26,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,29; 21,49</t>
+          <t>16,26; 21,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,01; 18,91</t>
+          <t>18,02; 18,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,58; 20,24</t>
+          <t>18,61; 20,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,11; 20,19</t>
+          <t>18,09; 20,02</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,39; 18,32</t>
+          <t>16,38; 18,33</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,34; 18,78</t>
+          <t>17,35; 18,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,57; 22,07</t>
+          <t>17,48; 21,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,1; 18,7</t>
+          <t>17,06; 18,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,22; 19,23</t>
+          <t>17,29; 19,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,44; 28,91</t>
+          <t>20,48; 28,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,82; 32,67</t>
+          <t>21,1; 35,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,8; 29,7</t>
+          <t>19,81; 29,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,68; 21,55</t>
+          <t>18,78; 21,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,14; 20,26</t>
+          <t>18,13; 20,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,66; 23,02</t>
+          <t>18,55; 22,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,02; 20,84</t>
+          <t>18,04; 21,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,68; 19,4</t>
+          <t>17,73; 19,38</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,0; 17,18</t>
+          <t>17,01; 17,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,52</t>
+          <t>17,21; 17,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1711,47 +1711,47 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,99; 17,27</t>
+          <t>16,99; 17,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,95; 18,37</t>
+          <t>17,95; 18,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,47; 19,1</t>
+          <t>18,5; 19,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,31; 18,93</t>
+          <t>18,31; 18,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,99; 18,63</t>
+          <t>17,07; 18,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,34; 17,53</t>
+          <t>17,35; 17,54</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17,69; 17,97</t>
+          <t>17,69; 17,98</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17,45; 17,74</t>
+          <t>17,46; 17,72</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,11; 17,65</t>
+          <t>17,12; 17,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q31A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q31A-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,39</t>
+          <t>16,38</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,16</t>
+          <t>16,35</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,31</t>
+          <t>16,37</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,73; 16,14</t>
+          <t>15,72; 16,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,94; 16,36</t>
+          <t>15,95; 16,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,95; 16,31</t>
+          <t>15,95; 16,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,03; 16,7</t>
+          <t>16,06; 16,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,24; 16,72</t>
+          <t>16,25; 16,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,02; 16,48</t>
+          <t>15,98; 16,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,23; 16,69</t>
+          <t>16,25; 16,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,7; 16,58</t>
+          <t>15,94; 16,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,99; 16,3</t>
+          <t>15,98; 16,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,04; 16,33</t>
+          <t>16,04; 16,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,13; 16,42</t>
+          <t>16,12; 16,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,07; 16,56</t>
+          <t>16,1; 16,61</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,78</t>
+          <t>16,79</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,88</t>
+          <t>16,92</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,82</t>
+          <t>16,84</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,73; 17,06</t>
+          <t>16,72; 17,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,8; 17,19</t>
+          <t>16,8; 17,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,66; 17,06</t>
+          <t>16,67; 17,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,52; 17,05</t>
+          <t>16,54; 17,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,2; 17,65</t>
+          <t>17,21; 17,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,19; 17,82</t>
+          <t>17,21; 17,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,17; 17,8</t>
+          <t>17,17; 17,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,56; 17,34</t>
+          <t>16,61; 17,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,93; 17,18</t>
+          <t>16,91; 17,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,97; 17,3</t>
+          <t>16,99; 17,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,91; 17,26</t>
+          <t>16,91; 17,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,6; 17,05</t>
+          <t>16,64; 17,07</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,2</t>
+          <t>17,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,37</t>
+          <t>18,38</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,6</t>
+          <t>17,63</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,01; 17,36</t>
+          <t>17,0; 17,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,06; 17,48</t>
+          <t>17,06; 17,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,86; 17,34</t>
+          <t>16,86; 17,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,94; 17,56</t>
+          <t>16,98; 17,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,98; 18,83</t>
+          <t>17,96; 18,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,36; 19,15</t>
+          <t>18,37; 19,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,57; 18,39</t>
+          <t>17,58; 18,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,96; 19,01</t>
+          <t>17,97; 18,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,42; 17,82</t>
+          <t>17,41; 17,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,6; 18,01</t>
+          <t>17,63; 18,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,19; 17,6</t>
+          <t>17,18; 17,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,36; 17,88</t>
+          <t>17,4; 17,91</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,1</t>
+          <t>17,2</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,74</t>
+          <t>17,84</t>
         </is>
       </c>
     </row>
@@ -1141,57 +1141,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,49; 18,07</t>
+          <t>17,49; 18,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,0; 17,56</t>
+          <t>17,01; 17,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,82; 17,53</t>
+          <t>16,95; 17,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,97; 20,08</t>
+          <t>18,96; 20,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,89; 20,17</t>
+          <t>18,95; 20,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,62; 19,82</t>
+          <t>18,65; 19,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,35; 19,6</t>
+          <t>18,37; 19,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,84; 18,31</t>
+          <t>17,81; 18,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,08; 18,7</t>
+          <t>18,08; 18,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,74; 18,31</t>
+          <t>17,77; 18,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,44; 18,04</t>
+          <t>17,55; 18,16</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,54</t>
+          <t>17,5</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,17</t>
+          <t>20,22</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,42</t>
+          <t>18,43</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,33; 17,98</t>
+          <t>17,31; 17,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,54; 19,03</t>
+          <t>17,56; 19,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,47 +1291,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,18; 18,03</t>
+          <t>17,13; 18,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,15; 20,72</t>
+          <t>19,2; 20,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,8; 22,3</t>
+          <t>19,83; 22,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,39; 21,78</t>
+          <t>19,37; 21,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,43; 21,34</t>
+          <t>19,42; 21,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,98; 18,68</t>
+          <t>17,98; 18,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,39; 19,63</t>
+          <t>18,4; 19,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,7; 18,6</t>
+          <t>17,7; 18,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,06; 18,9</t>
+          <t>18,06; 18,93</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17,11</t>
+          <t>17,14</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,25</t>
+          <t>21,18</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,19</t>
+          <t>18,24</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,71; 18,77</t>
+          <t>17,71; 18,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,52; 18,48</t>
+          <t>17,5; 18,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,92; 18,21</t>
+          <t>16,89; 18,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,81; 17,4</t>
+          <t>16,83; 17,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,5; 20,4</t>
+          <t>18,6; 20,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,93; 25,49</t>
+          <t>20,9; 25,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,7; 26,62</t>
+          <t>20,84; 26,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,26; 21,44</t>
+          <t>19,86; 23,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,02; 18,93</t>
+          <t>18,0; 18,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,61; 20,34</t>
+          <t>18,62; 20,19</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,09; 20,02</t>
+          <t>18,07; 20,09</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,38; 18,33</t>
+          <t>17,83; 18,88</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,94</t>
+          <t>17,96</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>20,16</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,39</t>
+          <t>18,46</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,35; 18,8</t>
+          <t>17,39; 18,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,48; 21,65</t>
+          <t>17,5; 21,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1571,47 +1571,47 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,29; 19,16</t>
+          <t>17,28; 19,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,48; 28,84</t>
+          <t>20,35; 28,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,1; 35,42</t>
+          <t>21,06; 33,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,81; 29,55</t>
+          <t>19,96; 30,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,78; 21,67</t>
+          <t>18,98; 21,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,13; 20,18</t>
+          <t>18,09; 20,2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,55; 22,75</t>
+          <t>18,6; 22,81</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,04; 21,2</t>
+          <t>18,11; 20,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,73; 19,38</t>
+          <t>17,8; 19,51</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17,12</t>
+          <t>17,15</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,01</t>
+          <t>18,6</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17,47</t>
+          <t>17,65</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,01; 17,2</t>
+          <t>17,0; 17,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,5</t>
+          <t>17,22; 17,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,89; 17,13</t>
+          <t>16,89; 17,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,99; 17,29</t>
+          <t>17,02; 17,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,95; 18,35</t>
+          <t>17,96; 18,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,16</t>
+          <t>18,48; 19,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,31; 18,9</t>
+          <t>18,3; 18,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,07; 18,64</t>
+          <t>18,34; 18,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,35; 17,54</t>
+          <t>17,34; 17,54</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17,69; 17,98</t>
+          <t>17,68; 17,97</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17,46; 17,72</t>
+          <t>17,45; 17,73</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,12; 17,67</t>
+          <t>17,52; 17,8</t>
         </is>
       </c>
     </row>
